--- a/data/trans_orig/IP07A09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,06%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36621</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59908</t>
+          <t>59055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29360</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38576</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50634</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21157</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>39683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>39806</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>80205</t>
+          <t>80458</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>95645</t>
+          <t>95724</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18725</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>35601</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>44324</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>58634</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>77296</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48563</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>69518</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99149</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>132525</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>80532</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>107756</t>
+          <t>107787</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>161759</t>
+          <t>159308</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>197985</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>182132</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>168651</t>
+          <t>169518</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>199292</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>332172</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>374275</t>
+          <t>373044</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18615</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>44116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60072</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75408</t>
+          <t>75908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40693</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24524</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>40290</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>34369</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>50044</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>67235</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>32385</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>40113</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>58155</t>
+          <t>58908</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>38417</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>41898</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>77473</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>57180</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>81200</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>148332</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>92671</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>56556</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132114</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>144453</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>173962</t>
+          <t>173556</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>165431</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>194380</t>
+          <t>195152</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>316022</t>
+          <t>316210</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>358680</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38104</t>
+          <t>37883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47949</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38948</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49512</t>
+          <t>49421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81109</t>
+          <t>81163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>95447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>49760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>26900</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27760</t>
+          <t>28235</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>34625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -16321,62 +16321,62 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7697</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3448</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16547,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16675,12 +16675,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>26943</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>51970</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>37514</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33342</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>47467</t>
+          <t>47248</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>66884</t>
+          <t>66303</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>46782</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40290</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>51008</t>
+          <t>49322</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>27280</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>35014</t>
+          <t>34388</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>39305</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>57700</t>
+          <t>57618</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78490</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>156118</t>
+          <t>156642</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>87837</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>116149</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109701</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>175493</t>
+          <t>176758</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>183003</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>159487</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>192044</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>320986</t>
+          <t>319149</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>363224</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
